--- a/artfynd/A 24233-2025 artfynd.xlsx
+++ b/artfynd/A 24233-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131740169</v>
       </c>
       <c r="B2" t="n">
-        <v>91849</v>
+        <v>91850</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24233-2025 artfynd.xlsx
+++ b/artfynd/A 24233-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131740169</v>
       </c>
       <c r="B2" t="n">
-        <v>91850</v>
+        <v>91853</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24233-2025 artfynd.xlsx
+++ b/artfynd/A 24233-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131740169</v>
       </c>
       <c r="B2" t="n">
-        <v>91853</v>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24233-2025 artfynd.xlsx
+++ b/artfynd/A 24233-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131740169</v>
       </c>
       <c r="B2" t="n">
-        <v>91859</v>
+        <v>91862</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24233-2025 artfynd.xlsx
+++ b/artfynd/A 24233-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131740169</v>
       </c>
       <c r="B2" t="n">
-        <v>91862</v>
+        <v>91867</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24233-2025 artfynd.xlsx
+++ b/artfynd/A 24233-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131740169</v>
       </c>
       <c r="B2" t="n">
-        <v>91910</v>
+        <v>91913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24233-2025 artfynd.xlsx
+++ b/artfynd/A 24233-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>131740169</v>
       </c>
       <c r="B2" t="n">
-        <v>91913</v>
+        <v>91995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -769,6 +769,112 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>113677071</v>
+      </c>
+      <c r="B3" t="n">
+        <v>4782</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tran-, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>566744</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6517293</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-11-28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-11-28</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>

--- a/artfynd/A 24233-2025 artfynd.xlsx
+++ b/artfynd/A 24233-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740169</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,8 +889,17 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113677071</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>